--- a/tests/acceptance/fixtures/xlsx/merges.xlsx
+++ b/tests/acceptance/fixtures/xlsx/merges.xlsx
@@ -53,7 +53,6 @@
   <fonts count="1">
     <font>
       <sz val="13"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
